--- a/FET_STEM/data/outreach.xlsx
+++ b/FET_STEM/data/outreach.xlsx
@@ -5,20 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sunwayeducationgroup-my.sharepoint.com/personal/tzeyings_sunway_edu_my/Documents/00_Academic/_FET STEM Project/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dr.sim/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{CF855E04-757F-754C-BDF8-D424625D6F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F71A1A65-B21D-AA44-B548-1DBD51B9E09C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD5D443-7695-804C-B2FF-32BC2126A1CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2060" yWindow="-20500" windowWidth="30260" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2040" yWindow="-20520" windowWidth="30260" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2026" sheetId="2" r:id="rId1"/>
-    <sheet name="2025 Outreach Workshops" sheetId="1" r:id="rId2"/>
+    <sheet name="2026" sheetId="1" r:id="rId1"/>
+    <sheet name="2025 Outreach Workshops" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2025 Outreach Workshops'!$A$1:$L$50</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$A$1:$L$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026'!$A$1:$L$47</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
     <author>Claude</author>
   </authors>
   <commentList>
-    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{AB3987D4-CC79-F547-B7D7-489848CC14EC}">
+    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -61,30 +61,8 @@
 </comments>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="708" uniqueCount="235">
   <si>
     <t>Date</t>
   </si>
@@ -122,6 +100,414 @@
     <t>Discipline</t>
   </si>
   <si>
+    <t>15:15 - 17:15</t>
+  </si>
+  <si>
+    <t>AUG Ipoh</t>
+  </si>
+  <si>
+    <t>SPM &amp; IGCSE</t>
+  </si>
+  <si>
+    <t>AI Programming</t>
+  </si>
+  <si>
+    <t>Nor Hafizah Mohamed Halip</t>
+  </si>
+  <si>
+    <t>UW-2-9</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>School visit – on campus</t>
+  </si>
+  <si>
+    <t>Computing</t>
+  </si>
+  <si>
+    <t>11:00 - 13:00</t>
+  </si>
+  <si>
+    <t>Open Day</t>
+  </si>
+  <si>
+    <t>Chemical Engineering Workshop</t>
+  </si>
+  <si>
+    <t>Yoon Li Wan, Ng Lik Yin</t>
+  </si>
+  <si>
+    <t>Chemistry Lab</t>
+  </si>
+  <si>
+    <t>Chemical</t>
+  </si>
+  <si>
+    <t>13:00 - 15:00</t>
+  </si>
+  <si>
+    <t>Computing Workshop</t>
+  </si>
+  <si>
+    <t>Faris Syahmi Samidi, Teoh Yun Xin</t>
+  </si>
+  <si>
+    <t>UW-2-6</t>
+  </si>
+  <si>
+    <t>14:00 - 17:00</t>
+  </si>
+  <si>
+    <t>SM Sains Pokok Sena</t>
+  </si>
+  <si>
+    <t>Form 5</t>
+  </si>
+  <si>
+    <t>Product Briefing</t>
+  </si>
+  <si>
+    <t>Sim Tze Ying, Lau Sian Lun</t>
+  </si>
+  <si>
+    <t>School visit – off campus</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>8:00 - 17:00</t>
+  </si>
+  <si>
+    <t>MRSM Kubang Pasu</t>
+  </si>
+  <si>
+    <t>MicroCode Workshop</t>
+  </si>
+  <si>
+    <t>SM Sains Sultan Abdul Halim</t>
+  </si>
+  <si>
+    <t>Mock Interview</t>
+  </si>
+  <si>
+    <t>9:30 - 12:30</t>
+  </si>
+  <si>
+    <t>MRSM Kuantan</t>
+  </si>
+  <si>
+    <t>Mock Interview &amp; Top Uni Workshop</t>
+  </si>
+  <si>
+    <t>Sim Tze Ying</t>
+  </si>
+  <si>
+    <t>Thinker Space</t>
+  </si>
+  <si>
+    <t>11:00 - 12:30</t>
+  </si>
+  <si>
+    <t>Pay Fong High School</t>
+  </si>
+  <si>
+    <t>SM3</t>
+  </si>
+  <si>
+    <t>Teoh Yun Xin</t>
+  </si>
+  <si>
+    <t>8:30 - 17:30</t>
+  </si>
+  <si>
+    <t>Diploma in Communication</t>
+  </si>
+  <si>
+    <t>Diploma</t>
+  </si>
+  <si>
+    <t>MakeCode Workshop</t>
+  </si>
+  <si>
+    <t>FR3</t>
+  </si>
+  <si>
+    <t>College Engagement</t>
+  </si>
+  <si>
+    <t>UW8-3</t>
+  </si>
+  <si>
+    <t>10:30 - 12:30</t>
+  </si>
+  <si>
+    <t>Foon Yew Kulai</t>
+  </si>
+  <si>
+    <t>UEC SM2/SM3</t>
+  </si>
+  <si>
+    <t>Mechanical Workshop (Gear)</t>
+  </si>
+  <si>
+    <t>Steven Hoo Choon Lih, Yoon Li Wan</t>
+  </si>
+  <si>
+    <t>Mechanical</t>
+  </si>
+  <si>
+    <t>Robotics Workshop</t>
+  </si>
+  <si>
+    <t>Richard Wong Teck Ken, Ng Lik Yin</t>
+  </si>
+  <si>
+    <t>Robotics</t>
+  </si>
+  <si>
+    <t>10:00 - 11:30</t>
+  </si>
+  <si>
+    <t>Foon Yew Seri Alam</t>
+  </si>
+  <si>
+    <t>14:00 - 15:40</t>
+  </si>
+  <si>
+    <t>Foon Yew JB</t>
+  </si>
+  <si>
+    <t>11:10 - 12:40</t>
+  </si>
+  <si>
+    <t>RE2 Ipoh</t>
+  </si>
+  <si>
+    <t>Faris Syahmi Samidi</t>
+  </si>
+  <si>
+    <t>UWCL2-2</t>
+  </si>
+  <si>
+    <t>15:10 - 16:40</t>
+  </si>
+  <si>
+    <t>UEC SM3</t>
+  </si>
+  <si>
+    <t>EE Workshop</t>
+  </si>
+  <si>
+    <t>Ranjit Singh Sarban Singh</t>
+  </si>
+  <si>
+    <t>Electronic Engineering Lab</t>
+  </si>
+  <si>
+    <t>Electrical &amp; Electronic</t>
+  </si>
+  <si>
+    <t>9:30 - 11:00</t>
+  </si>
+  <si>
+    <t>Foon Yew Setia Alam</t>
+  </si>
+  <si>
+    <t>Chemical Workshop</t>
+  </si>
+  <si>
+    <t>Chua Bee Lin, Tan Siew Lan, Nurhazwani Rozadin</t>
+  </si>
+  <si>
+    <t>Yoon Li Wan</t>
+  </si>
+  <si>
+    <t>14:40 - 16:10</t>
+  </si>
+  <si>
+    <t>Chung Ling Private High School</t>
+  </si>
+  <si>
+    <t>SM3 &amp; Y11</t>
+  </si>
+  <si>
+    <t>Foo Jinny</t>
+  </si>
+  <si>
+    <t>15:30 - 17:00</t>
+  </si>
+  <si>
+    <t>Civil Workshop</t>
+  </si>
+  <si>
+    <t>Structural Workshop</t>
+  </si>
+  <si>
+    <t>Ean Lee Woen, Tracy Wong Leh Xin, Tan Tee How</t>
+  </si>
+  <si>
+    <t>Solid Mechanics &amp; Materials Lab</t>
+  </si>
+  <si>
+    <t>Civil</t>
+  </si>
+  <si>
+    <t>Mechanical Workshop</t>
+  </si>
+  <si>
+    <t>Build Your Own Heat Exchanger</t>
+  </si>
+  <si>
+    <t>Satesh Narayana Namasivayam</t>
+  </si>
+  <si>
+    <t>Engineering Project Lab</t>
+  </si>
+  <si>
+    <t>CAD Workshop</t>
+  </si>
+  <si>
+    <t>Idea &gt; 3D</t>
+  </si>
+  <si>
+    <t>Steven Hoo Choon Lih</t>
+  </si>
+  <si>
+    <t>ACL1</t>
+  </si>
+  <si>
+    <t>Mechanical / CAD</t>
+  </si>
+  <si>
+    <t>14:45 - 15:45</t>
+  </si>
+  <si>
+    <t>MRSM Pasir Tumboh SLE</t>
+  </si>
+  <si>
+    <t>Interview and Resume Talk</t>
+  </si>
+  <si>
+    <t>Anwar P.P. Abdul Majeed</t>
+  </si>
+  <si>
+    <t>Sunway Pre-U</t>
+  </si>
+  <si>
+    <t>Pre-U</t>
+  </si>
+  <si>
+    <t>Data Analytics</t>
+  </si>
+  <si>
+    <t>Samuel Mofoluwa Ajibade</t>
+  </si>
+  <si>
+    <t>AI Workshop</t>
+  </si>
+  <si>
+    <t>AI Made Easy with Ornage</t>
+  </si>
+  <si>
+    <t>Data Analytics Workshop</t>
+  </si>
+  <si>
+    <t>Introduction to Data Analytics and Visualisation with Microsoft Power BI</t>
+  </si>
+  <si>
+    <t>ACL2</t>
+  </si>
+  <si>
+    <t>10:00 - 13:00</t>
+  </si>
+  <si>
+    <t>MRSM Alor Gajah</t>
+  </si>
+  <si>
+    <t>Career in Engineering and IT</t>
+  </si>
+  <si>
+    <t>Lau Sian Lun, Sim Tze Ying, Nor Hafizah Mohamed Halip</t>
+  </si>
+  <si>
+    <t>10:00 - 16:00</t>
+  </si>
+  <si>
+    <t>Teoh Yun Xin, Claymond Lim Wei Xiang, Vimal Angela Thiviyanathan</t>
+  </si>
+  <si>
+    <t>ACL 1 &amp; 2</t>
+  </si>
+  <si>
+    <t>Civil Engineering Workshop</t>
+  </si>
+  <si>
+    <t>Ean Lee Woen, Tracy Wong Leh Xin, Hayana Dullah</t>
+  </si>
+  <si>
+    <t>Wan Siti Halimatul Munirah Wan Yahya @ Wan Ahmad, Wan Siti Nur Aiza Wan Othman</t>
+  </si>
+  <si>
+    <t>Ayu Haslija</t>
+  </si>
+  <si>
+    <t>13:45 - 15:45</t>
+  </si>
+  <si>
+    <t>SM Sains Raja Tun Azlan Shah</t>
+  </si>
+  <si>
+    <t>A-Level</t>
+  </si>
+  <si>
+    <t>Rooftop Terrace</t>
+  </si>
+  <si>
+    <t>Foundation in Arts</t>
+  </si>
+  <si>
+    <t>Foundation</t>
+  </si>
+  <si>
+    <t>8:30 - 16:00</t>
+  </si>
+  <si>
+    <t>SM Sains Kepala Batas</t>
+  </si>
+  <si>
+    <t>Mock Interview, Resume &amp; Interview Talk, and Careers in Computing and Technology Workshop</t>
+  </si>
+  <si>
+    <t>Sim Tze Ying, Lau Sian Lun, Nor Hafizah Mohamed Halip</t>
+  </si>
+  <si>
+    <t>SJKC Pandamaran A</t>
+  </si>
+  <si>
+    <t>Primary</t>
+  </si>
+  <si>
+    <t>Vimal Angela Thiviyanathan, Sim Tze Ying, Nor Hafizah Mohamed Halip</t>
+  </si>
+  <si>
+    <t>SJKC Damansara Jaya</t>
+  </si>
+  <si>
+    <t>SJKT Simpang Lima</t>
+  </si>
+  <si>
+    <t>Vimal Angela Thiviyanathan, Sim Tze Ying, Nor Hafizah Mohamed Halip, Tan Ee Xion</t>
+  </si>
+  <si>
+    <t>Sekolah Kebangsaan Sungai Judah</t>
+  </si>
+  <si>
+    <t>ACL 2</t>
+  </si>
+  <si>
     <t>Han Chiang High School</t>
   </si>
   <si>
@@ -131,12 +517,6 @@
     <t>Maisarah Mansor</t>
   </si>
   <si>
-    <t>School visit – off campus</t>
-  </si>
-  <si>
-    <t>Computing</t>
-  </si>
-  <si>
     <t>Kolej MARA</t>
   </si>
   <si>
@@ -149,24 +529,15 @@
     <t>Nor Akmar Mohd Yahya</t>
   </si>
   <si>
-    <t>General</t>
-  </si>
-  <si>
     <t>International School</t>
   </si>
   <si>
-    <t>8:00 - 17:00</t>
-  </si>
-  <si>
     <t>MRSM KKB</t>
   </si>
   <si>
     <t>What's after SPM</t>
   </si>
   <si>
-    <t>Sim Tze Ying, Lau Sian Lun</t>
-  </si>
-  <si>
     <t>MRSM Schools</t>
   </si>
   <si>
@@ -176,30 +547,9 @@
     <t>Think Technology</t>
   </si>
   <si>
-    <t>15:15 - 17:15</t>
-  </si>
-  <si>
-    <t>Form 5</t>
-  </si>
-  <si>
-    <t>AI Programming</t>
-  </si>
-  <si>
     <t>Noor Hafizah Hassan, Foo Jinny</t>
   </si>
   <si>
-    <t>UW-2-9</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>School visit – on campus</t>
-  </si>
-  <si>
-    <t>Robotics</t>
-  </si>
-  <si>
     <t>Chia Wai Chong</t>
   </si>
   <si>
@@ -209,9 +559,6 @@
     <t>SIS</t>
   </si>
   <si>
-    <t>AI Workshop</t>
-  </si>
-  <si>
     <t>8:30 - 9:30</t>
   </si>
   <si>
@@ -221,9 +568,6 @@
     <t>Tan Ee Xion</t>
   </si>
   <si>
-    <t>ACL2</t>
-  </si>
-  <si>
     <t>1.(Ian Foong, Ying Qin, ZiYi)</t>
   </si>
   <si>
@@ -248,9 +592,6 @@
     <t>14:00 - 15:00</t>
   </si>
   <si>
-    <t>Anwar P.P. Abdul Majeed</t>
-  </si>
-  <si>
     <t>4. Bouchikhi Shareefah, Gan Jayci</t>
   </si>
   <si>
@@ -284,9 +625,6 @@
     <t>6.  Vanice</t>
   </si>
   <si>
-    <t>Teoh Yun Xin</t>
-  </si>
-  <si>
     <t>UW2-1</t>
   </si>
   <si>
@@ -302,15 +640,6 @@
     <t>Riady Siswoyo Jo</t>
   </si>
   <si>
-    <t>Sim Tze Ying</t>
-  </si>
-  <si>
-    <t>ACL1</t>
-  </si>
-  <si>
-    <t>Faris Syahmi Samidi</t>
-  </si>
-  <si>
     <t>10. Vanice Chong Yun Ni, Sofea Qistina</t>
   </si>
   <si>
@@ -320,15 +649,6 @@
     <t>Mito First High School</t>
   </si>
   <si>
-    <t>CAD Workshop</t>
-  </si>
-  <si>
-    <t>Steven Hoo Choon Lih</t>
-  </si>
-  <si>
-    <t>Mechanical / CAD</t>
-  </si>
-  <si>
     <t>EE Lab</t>
   </si>
   <si>
@@ -338,9 +658,6 @@
     <t>Tan Tee How</t>
   </si>
   <si>
-    <t>Civil</t>
-  </si>
-  <si>
     <t>10:00 - 12:00</t>
   </si>
   <si>
@@ -365,24 +682,12 @@
     <t>Wei Liang, Seru</t>
   </si>
   <si>
-    <t>10:30 - 12:30</t>
-  </si>
-  <si>
     <t>Confucian High School</t>
   </si>
   <si>
     <t>Soap Workshop</t>
   </si>
   <si>
-    <t>Yoon Li Wan</t>
-  </si>
-  <si>
-    <t>Chemistry Lab</t>
-  </si>
-  <si>
-    <t>Chemical</t>
-  </si>
-  <si>
     <t>Kee Chia Ching</t>
   </si>
   <si>
@@ -422,24 +727,12 @@
     <t>Ranjit Singh Sarban Singh, Chia Wai Chong</t>
   </si>
   <si>
-    <t>Electrical &amp; Electronic</t>
-  </si>
-  <si>
-    <t>10:00 - 11:30</t>
-  </si>
-  <si>
     <t>Sri KDU Private School</t>
   </si>
   <si>
     <t>Form 3</t>
   </si>
   <si>
-    <t>Foo Jinny</t>
-  </si>
-  <si>
-    <t>10:00 - 16:00</t>
-  </si>
-  <si>
     <t>Open Day Workshop</t>
   </si>
   <si>
@@ -452,9 +745,6 @@
     <t>FET</t>
   </si>
   <si>
-    <t>Open Day</t>
-  </si>
-  <si>
     <t>Exploring Civil Engineering through Experiments</t>
   </si>
   <si>
@@ -473,295 +763,10 @@
     <t>SM Sains Segamat</t>
   </si>
   <si>
-    <t>Mock Interview</t>
-  </si>
-  <si>
     <t>SM Sains Taiping</t>
   </si>
   <si>
-    <t>Robotics Workshop</t>
-  </si>
-  <si>
-    <t>AUG Ipoh</t>
-  </si>
-  <si>
-    <t>SPM &amp; IGCSE</t>
-  </si>
-  <si>
-    <t>Nor Hafizah Mohamed Halip</t>
-  </si>
-  <si>
-    <t>11:00 - 13:00</t>
-  </si>
-  <si>
-    <t>Chemical Engineering Workshop</t>
-  </si>
-  <si>
-    <t>Yoon Li Wan, Ng Lik Yin</t>
-  </si>
-  <si>
-    <t>13:00 - 15:00</t>
-  </si>
-  <si>
-    <t>Computing Workshop</t>
-  </si>
-  <si>
-    <t>Faris Syahmi Samidi, Teoh Yun Xin</t>
-  </si>
-  <si>
-    <t>UW-2-6</t>
-  </si>
-  <si>
-    <t>14:00 - 17:00</t>
-  </si>
-  <si>
-    <t>SM Sains Pokok Sena</t>
-  </si>
-  <si>
-    <t>Product Briefing</t>
-  </si>
-  <si>
-    <t>MRSM Kubang Pasu</t>
-  </si>
-  <si>
-    <t>MicroCode Workshop</t>
-  </si>
-  <si>
-    <t>SM Sains Sultan Abdul Halim</t>
-  </si>
-  <si>
-    <t>9:30 - 12:30</t>
-  </si>
-  <si>
-    <t>MRSM Kuantan</t>
-  </si>
-  <si>
-    <t>Mock Interview &amp; Top Uni Workshop</t>
-  </si>
-  <si>
-    <t>Thinker Space</t>
-  </si>
-  <si>
-    <t>11:00 - 12:30</t>
-  </si>
-  <si>
-    <t>Pay Fong High School</t>
-  </si>
-  <si>
-    <t>SM3</t>
-  </si>
-  <si>
-    <t>8:30 - 17:30</t>
-  </si>
-  <si>
-    <t>Diploma in Communication</t>
-  </si>
-  <si>
-    <t>Diploma</t>
-  </si>
-  <si>
-    <t>MakeCode Workshop</t>
-  </si>
-  <si>
-    <t>FR3</t>
-  </si>
-  <si>
-    <t>College Engagement</t>
-  </si>
-  <si>
-    <t>UW8-3</t>
-  </si>
-  <si>
-    <t>Foon Yew Kulai</t>
-  </si>
-  <si>
-    <t>UEC SM2/SM3</t>
-  </si>
-  <si>
-    <t>Mechanical Workshop (Gear)</t>
-  </si>
-  <si>
-    <t>Steven Hoo Choon Lih, Yoon Li Wan</t>
-  </si>
-  <si>
-    <t>Mechanical</t>
-  </si>
-  <si>
-    <t>Richard Wong Teck Ken, Ng Lik Yin</t>
-  </si>
-  <si>
-    <t>Foon Yew Seri Alam</t>
-  </si>
-  <si>
-    <t>14:00 - 15:40</t>
-  </si>
-  <si>
-    <t>Foon Yew JB</t>
-  </si>
-  <si>
-    <t>11:10 - 12:40</t>
-  </si>
-  <si>
-    <t>RE2 Ipoh</t>
-  </si>
-  <si>
-    <t>UWCL2-2</t>
-  </si>
-  <si>
-    <t>15:10 - 16:40</t>
-  </si>
-  <si>
-    <t>UEC SM3</t>
-  </si>
-  <si>
-    <t>EE Workshop</t>
-  </si>
-  <si>
-    <t>Ranjit Singh Sarban Singh</t>
-  </si>
-  <si>
-    <t>Electronic Engineering Lab</t>
-  </si>
-  <si>
-    <t>9:30 - 11:00</t>
-  </si>
-  <si>
-    <t>Foon Yew Setia Alam</t>
-  </si>
-  <si>
-    <t>Chemical Workshop</t>
-  </si>
-  <si>
-    <t>Chua Bee Lin, Tan Siew Lan, Nurhazwani Rozadin</t>
-  </si>
-  <si>
-    <t>14:40 - 16:10</t>
-  </si>
-  <si>
-    <t>Chung Ling Private High School</t>
-  </si>
-  <si>
-    <t>SM3 &amp; Y11</t>
-  </si>
-  <si>
-    <t>15:30 - 17:00</t>
-  </si>
-  <si>
-    <t>Civil Workshop</t>
-  </si>
-  <si>
-    <t>Structural Workshop</t>
-  </si>
-  <si>
-    <t>Ean Lee Woen, Tracy Wong Leh Xin, Tan Tee How</t>
-  </si>
-  <si>
-    <t>Solid Mechanics &amp; Materials Lab</t>
-  </si>
-  <si>
-    <t>Mechanical Workshop</t>
-  </si>
-  <si>
-    <t>Build Your Own Heat Exchanger</t>
-  </si>
-  <si>
-    <t>Satesh Narayana Namasivayam</t>
-  </si>
-  <si>
-    <t>Engineering Project Lab</t>
-  </si>
-  <si>
-    <t>Idea &gt; 3D</t>
-  </si>
-  <si>
-    <t>14:45 - 15:45</t>
-  </si>
-  <si>
-    <t>MRSM Pasir Tumboh SLE</t>
-  </si>
-  <si>
-    <t>Interview and Resume Talk</t>
-  </si>
-  <si>
-    <t>Sunway Pre-U</t>
-  </si>
-  <si>
-    <t>Pre-U</t>
-  </si>
-  <si>
-    <t>Data Analytics</t>
-  </si>
-  <si>
-    <t>Samuel Mofoluwa Ajibade</t>
-  </si>
-  <si>
-    <t>AI Made Easy with Ornage</t>
-  </si>
-  <si>
-    <t>Data Analytics Workshop</t>
-  </si>
-  <si>
-    <t>Introduction to Data Analytics and Visualisation with Microsoft Power BI</t>
-  </si>
-  <si>
-    <t>10:00 - 13:00</t>
-  </si>
-  <si>
-    <t>MRSM Alor Gajah</t>
-  </si>
-  <si>
-    <t>Career in Engineering and IT</t>
-  </si>
-  <si>
-    <t>Lau Sian Lun, Sim Tze Ying, Nor Hafizah Mohamed Halip</t>
-  </si>
-  <si>
-    <t>Teoh Yun Xin, Claymond Lim Wei Xiang, Vimal Angela Thiviyanathan</t>
-  </si>
-  <si>
-    <t>ACL 1 &amp; 2</t>
-  </si>
-  <si>
-    <t>Civil Engineering Workshop</t>
-  </si>
-  <si>
-    <t>Ean Lee Woen, Tracy Wong Leh Xin, Hayana Dullah</t>
-  </si>
-  <si>
-    <t>Wan Siti Halimatul Munirah Wan Yahya @ Wan Ahmad, Wan Siti Nur Aiza Wan Othman</t>
-  </si>
-  <si>
-    <t>Ayu Haslija</t>
-  </si>
-  <si>
-    <t>13:45 - 15:45</t>
-  </si>
-  <si>
-    <t>SM Sains Raja Tun Azlan Shah</t>
-  </si>
-  <si>
-    <t>A-Level</t>
-  </si>
-  <si>
-    <t>Rooftop Terrace</t>
-  </si>
-  <si>
-    <t>Foundation in Arts</t>
-  </si>
-  <si>
-    <t>Foundation</t>
-  </si>
-  <si>
-    <t>8:30 - 16:00</t>
-  </si>
-  <si>
-    <t>SM Sains Kepala Batas</t>
-  </si>
-  <si>
-    <t>Mock Interview, Resume &amp; Interview Talk, and Careers in Computing and Technology Workshop</t>
-  </si>
-  <si>
-    <t>Sim Tze Ying, Lau Sian Lun, Nor Hafizah Mohamed Halip</t>
+    <t>AI and Gender Bias</t>
   </si>
 </sst>
 </file>
@@ -795,7 +800,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -805,6 +810,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -850,7 +860,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -881,6 +891,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1183,8 +1196,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7644423-B5AA-3F41-8858-B6CE6811F93D}">
-  <dimension ref="A1:O43"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
@@ -1194,14 +1207,14 @@
     <col min="5" max="5" width="11.5" customWidth="1"/>
     <col min="6" max="6" width="29.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="25.83203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" style="10"/>
+    <col min="8" max="8" width="8.83203125" style="10" customWidth="1"/>
     <col min="9" max="9" width="11.5" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.5" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="13.5" customWidth="1"/>
     <col min="14" max="14" width="24.1640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1238,8 +1251,8 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="7" t="str" cm="1">
-        <f t="array" ref="N1:O27">_xlfn.LET(
+      <c r="N1" s="7" t="str">
+        <f t="array" ref="N1:O34">_xlfn.LET(
 _xlpm.raw, G1:G57,
 _xlpm.all\_names, _xlfn.TOCOL(TRIM(_xlfn.TEXTSPLIT(_xlfn.TEXTJOIN(",", TRUE, _xlpm.raw), ",")), 3),
 _xlpm.uniques, _xlfn.UNIQUE(_xlpm.all\_names),
@@ -1252,78 +1265,78 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>46027</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="D2" s="3">
         <v>18</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>134</v>
+        <v>16</v>
       </c>
       <c r="H2" s="9">
         <v>4.8</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N2" s="8" t="str">
         <v>Nor Hafizah Mohamed Halip</v>
       </c>
       <c r="O2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>46039</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>135</v>
+        <v>21</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="5"/>
       <c r="F3" s="4" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>137</v>
+        <v>24</v>
       </c>
       <c r="H3" s="9"/>
       <c r="I3" s="4" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="5" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="N3" s="8" t="str">
         <v>Yoon Li Wan</v>
@@ -1332,34 +1345,34 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>46039</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="5"/>
       <c r="F4" s="4" t="s">
-        <v>139</v>
+        <v>28</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>140</v>
+        <v>29</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="4" t="s">
-        <v>141</v>
+        <v>30</v>
       </c>
       <c r="J4" s="5"/>
       <c r="K4" s="5" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N4" s="8" t="str">
         <v>Ng Lik Yin</v>
@@ -1368,38 +1381,38 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>46042</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>142</v>
+        <v>31</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>143</v>
+        <v>32</v>
       </c>
       <c r="D5" s="3">
         <v>120</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>144</v>
+        <v>34</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="4" t="s">
-        <v>143</v>
+        <v>32</v>
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="N5" s="8" t="str">
         <v>Faris Syahmi Samidi</v>
@@ -1408,38 +1421,38 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>46043</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="D6" s="3">
         <v>120</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="4" t="s">
-        <v>145</v>
+        <v>39</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N6" s="8" t="str">
         <v>Teoh Yun Xin</v>
@@ -1448,80 +1461,80 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>46044</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="D7" s="3">
         <v>120</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>129</v>
+        <v>42</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="4" t="s">
-        <v>147</v>
+        <v>41</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="N7" s="8" t="str">
         <v>Sim Tze Ying</v>
       </c>
       <c r="O7">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>46064</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>148</v>
+        <v>43</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>149</v>
+        <v>44</v>
       </c>
       <c r="D8" s="3">
         <v>25</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>150</v>
+        <v>45</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="H8" s="9">
         <v>4.8</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>151</v>
+        <v>47</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="N8" s="8" t="str">
         <v>Lau Sian Lun</v>
@@ -1530,40 +1543,40 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>46081</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>152</v>
+        <v>48</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>153</v>
+        <v>49</v>
       </c>
       <c r="D9" s="3">
         <v>35</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="H9" s="9">
         <v>4.0999999999999996</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="5" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N9" s="8" t="str">
         <v>Steven Hoo Choon Lih</v>
@@ -1572,38 +1585,38 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>46093</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>155</v>
+        <v>52</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>156</v>
+        <v>53</v>
       </c>
       <c r="D10" s="3">
         <v>35</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>157</v>
+        <v>54</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="4" t="s">
-        <v>159</v>
+        <v>56</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5" t="s">
-        <v>160</v>
+        <v>57</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N10" s="8" t="str">
         <v>Richard Wong Teck Ken</v>
@@ -1612,38 +1625,38 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>46094</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>155</v>
+        <v>52</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>156</v>
+        <v>53</v>
       </c>
       <c r="D11" s="3">
         <v>35</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>157</v>
+        <v>54</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="4" t="s">
-        <v>161</v>
+        <v>58</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5" t="s">
-        <v>160</v>
+        <v>57</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N11" s="8" t="str">
         <v>Ranjit Singh Sarban Singh</v>
@@ -1652,38 +1665,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>46097</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>162</v>
+        <v>60</v>
       </c>
       <c r="D12" s="3">
         <v>70</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>163</v>
+        <v>61</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>164</v>
+        <v>62</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>165</v>
+        <v>63</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" s="4" t="s">
-        <v>162</v>
+        <v>60</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>166</v>
+        <v>64</v>
       </c>
       <c r="N12" s="8" t="str">
         <v>Chua Bee Lin</v>
@@ -1692,38 +1705,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>46097</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>138</v>
+        <v>27</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>162</v>
+        <v>60</v>
       </c>
       <c r="D13" s="3">
         <v>70</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>163</v>
+        <v>61</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" s="4" t="s">
-        <v>162</v>
+        <v>60</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="N13" s="8" t="str">
         <v>Tan Siew Lan</v>
@@ -1732,38 +1745,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>46098</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>168</v>
+        <v>69</v>
       </c>
       <c r="D14" s="3">
         <v>80</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>163</v>
+        <v>61</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" s="4" t="s">
-        <v>162</v>
+        <v>60</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="N14" s="8" t="str">
         <v>Nurhazwani Rozadin</v>
@@ -1772,38 +1785,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>46098</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>168</v>
+        <v>69</v>
       </c>
       <c r="D15" s="3">
         <v>80</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>163</v>
+        <v>61</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>164</v>
+        <v>62</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>165</v>
+        <v>63</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="4" t="s">
-        <v>162</v>
+        <v>60</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>166</v>
+        <v>64</v>
       </c>
       <c r="N15" s="8" t="str">
         <v>Foo Jinny</v>
@@ -1812,38 +1825,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>46098</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>169</v>
+        <v>70</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>170</v>
+        <v>71</v>
       </c>
       <c r="D16" s="3">
         <v>50</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>163</v>
+        <v>61</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="H16" s="9"/>
       <c r="I16" s="4" t="s">
-        <v>162</v>
+        <v>60</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="N16" s="8" t="str">
         <v>Ean Lee Woen</v>
@@ -1852,38 +1865,38 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>46098</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>169</v>
+        <v>70</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>170</v>
+        <v>71</v>
       </c>
       <c r="D17" s="3">
         <v>50</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>163</v>
+        <v>61</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>164</v>
+        <v>62</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>165</v>
+        <v>63</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" s="4" t="s">
-        <v>162</v>
+        <v>60</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>166</v>
+        <v>64</v>
       </c>
       <c r="N17" s="8" t="str">
         <v>Tracy Wong Leh Xin</v>
@@ -1892,24 +1905,24 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>46106</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>172</v>
+        <v>73</v>
       </c>
       <c r="D18" s="3">
         <v>40</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>74</v>
@@ -1918,14 +1931,14 @@
         <v>4.6500000000000004</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N18" s="8" t="str">
         <v>Tan Tee How</v>
@@ -1934,38 +1947,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>46106</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>174</v>
+        <v>76</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>162</v>
+        <v>60</v>
       </c>
       <c r="D19" s="3">
         <v>25</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>176</v>
+        <v>78</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>177</v>
+        <v>79</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="4" t="s">
-        <v>178</v>
+        <v>80</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="N19" s="8" t="str">
         <v>Satesh Narayana Namasivayam</v>
@@ -1974,38 +1987,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>46107</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="D20" s="3">
         <v>20</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>181</v>
+        <v>84</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>182</v>
+        <v>85</v>
       </c>
       <c r="H20" s="9"/>
       <c r="I20" s="4" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="N20" s="8" t="str">
         <v>Anwar P.P. Abdul Majeed</v>
@@ -2014,38 +2027,38 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>46107</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>179</v>
+        <v>82</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>180</v>
+        <v>83</v>
       </c>
       <c r="D21" s="3">
         <v>20</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>175</v>
+        <v>77</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>181</v>
+        <v>84</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="4" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="N21" s="8" t="str">
         <v>Samuel Mofoluwa Ajibade</v>
@@ -2054,27 +2067,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>46107</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>183</v>
+        <v>87</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>184</v>
+        <v>88</v>
       </c>
       <c r="D22" s="3">
         <v>40</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>185</v>
+        <v>89</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="H22" s="9">
         <v>4.66</v>
@@ -2082,10 +2095,10 @@
       <c r="I22" s="4"/>
       <c r="J22" s="5"/>
       <c r="K22" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N22" s="8" t="str">
         <v>Claymond Lim Wei Xiang</v>
@@ -2094,70 +2107,70 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>46113</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>186</v>
+        <v>91</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>187</v>
+        <v>92</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="5"/>
       <c r="F23" s="4" t="s">
-        <v>188</v>
+        <v>93</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>189</v>
+        <v>94</v>
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="4" t="s">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="N23" s="8" t="str">
         <v>Vimal Angela Thiviyanathan</v>
       </c>
       <c r="O23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>46113</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>186</v>
+        <v>91</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>191</v>
+        <v>97</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="5"/>
       <c r="F24" s="4" t="s">
-        <v>192</v>
+        <v>98</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>193</v>
+        <v>99</v>
       </c>
       <c r="H24" s="9"/>
       <c r="I24" s="4" t="s">
-        <v>194</v>
+        <v>100</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>166</v>
+        <v>64</v>
       </c>
       <c r="N24" s="8" t="str">
         <v>Hayana Dullah</v>
@@ -2166,34 +2179,34 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>46113</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>186</v>
+        <v>91</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="5"/>
       <c r="F25" s="4" t="s">
-        <v>195</v>
+        <v>102</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="4" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="N25" s="8" t="str">
         <v>Wan Siti Halimatul Munirah Wan Yahya @ Wan Ahmad</v>
@@ -2202,36 +2215,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="32" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>46114</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>196</v>
+        <v>106</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>197</v>
+        <v>107</v>
       </c>
       <c r="D26" s="3">
         <v>26</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>198</v>
+        <v>108</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="H26" s="9"/>
       <c r="I26" s="4"/>
       <c r="J26" s="5"/>
       <c r="K26" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="N26" s="8" t="str">
         <v>Wan Siti Nur Aiza Wan Othman</v>
@@ -2240,27 +2253,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>46114</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>186</v>
+        <v>91</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>199</v>
+        <v>110</v>
       </c>
       <c r="D27" s="3">
         <v>40</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>200</v>
+        <v>111</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>140</v>
+        <v>29</v>
       </c>
       <c r="H27" s="9">
         <v>4.92</v>
@@ -2268,10 +2281,10 @@
       <c r="I27" s="4"/>
       <c r="J27" s="5"/>
       <c r="K27" s="5" t="s">
-        <v>160</v>
+        <v>57</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N27" s="8" t="str">
         <v>Ayu Haslija</v>
@@ -2285,31 +2298,37 @@
         <v>46114</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>186</v>
+        <v>91</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>199</v>
+        <v>110</v>
       </c>
       <c r="D28" s="3">
         <v>40</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>200</v>
+        <v>111</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>201</v>
+        <v>112</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>202</v>
+        <v>113</v>
       </c>
       <c r="H28" s="9"/>
       <c r="I28" s="4"/>
       <c r="J28" s="5"/>
       <c r="K28" s="5" t="s">
-        <v>160</v>
+        <v>57</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="N28" s="8" t="str">
+        <v>Tan Ee Xion</v>
+      </c>
+      <c r="O28">
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.2">
@@ -2317,15 +2336,15 @@
         <v>46114</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>186</v>
+        <v>91</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="5"/>
       <c r="F29" s="4" t="s">
-        <v>203</v>
+        <v>115</v>
       </c>
       <c r="G29" s="4" t="s">
         <v>74</v>
@@ -2334,475 +2353,639 @@
         <v>4.92</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5" t="s">
-        <v>160</v>
+        <v>57</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="N29" s="8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="O29" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>46114</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>186</v>
+        <v>91</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>204</v>
+        <v>116</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="5"/>
       <c r="F30" s="4" t="s">
-        <v>205</v>
+        <v>117</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>202</v>
+        <v>113</v>
       </c>
       <c r="H30" s="9"/>
       <c r="I30" s="4" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="J30" s="5"/>
       <c r="K30" s="5" t="s">
-        <v>160</v>
+        <v>57</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" ht="28" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="N30" s="8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="O30" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>46119</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>206</v>
+        <v>119</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>207</v>
+        <v>120</v>
       </c>
       <c r="D31" s="3">
         <v>40</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>208</v>
+        <v>121</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>209</v>
+        <v>122</v>
       </c>
       <c r="H31" s="9">
         <v>4.9400000000000004</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>151</v>
+        <v>47</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+      <c r="N31" s="8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="O31" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>46123</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="5"/>
       <c r="F32" s="4" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>210</v>
+        <v>124</v>
       </c>
       <c r="H32" s="9"/>
       <c r="I32" s="4" t="s">
-        <v>211</v>
+        <v>125</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+      <c r="N32" s="8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="O32" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>46123</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="5"/>
       <c r="F33" s="4" t="s">
-        <v>212</v>
+        <v>126</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>213</v>
+        <v>127</v>
       </c>
       <c r="H33" s="9"/>
       <c r="I33" s="4" t="s">
-        <v>194</v>
+        <v>100</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="L33" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+      <c r="N33" s="8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="O33" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>46123</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="5"/>
       <c r="F34" s="4" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="H34" s="9"/>
       <c r="I34" s="4" t="s">
-        <v>194</v>
+        <v>100</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="L34" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+      <c r="N34" s="8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="O34" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>46124</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="5"/>
       <c r="F35" s="4" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>214</v>
+        <v>128</v>
       </c>
       <c r="H35" s="9"/>
       <c r="I35" s="4" t="s">
-        <v>211</v>
+        <v>125</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>46124</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="5"/>
       <c r="F36" s="4" t="s">
-        <v>212</v>
+        <v>126</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>213</v>
+        <v>127</v>
       </c>
       <c r="H36" s="9"/>
       <c r="I36" s="4" t="s">
-        <v>194</v>
+        <v>100</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="L36" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>46124</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="5"/>
       <c r="F37" s="4" t="s">
-        <v>136</v>
+        <v>23</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>215</v>
+        <v>129</v>
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="4" t="s">
-        <v>194</v>
+        <v>100</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="L37" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="42" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>46135</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>216</v>
+        <v>130</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>217</v>
+        <v>131</v>
       </c>
       <c r="D38" s="3">
         <v>112</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H38" s="9"/>
       <c r="I38" s="4" t="s">
-        <v>217</v>
+        <v>131</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L38" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>46191</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>155</v>
+        <v>52</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>218</v>
+        <v>132</v>
       </c>
       <c r="D39" s="3">
         <v>25</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>218</v>
+        <v>132</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="H39" s="9"/>
       <c r="I39" s="4" t="s">
-        <v>219</v>
+        <v>133</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5" t="s">
-        <v>160</v>
+        <v>57</v>
       </c>
       <c r="L39" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>46192</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>155</v>
+        <v>52</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>218</v>
+        <v>132</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="5" t="s">
-        <v>218</v>
+        <v>132</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="H40" s="9">
         <v>4.62</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>151</v>
+        <v>47</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="5" t="s">
-        <v>160</v>
+        <v>57</v>
       </c>
       <c r="L40" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>46195</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>155</v>
+        <v>52</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>220</v>
+        <v>134</v>
       </c>
       <c r="D41" s="3">
         <v>60</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>221</v>
+        <v>135</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="H41" s="9"/>
       <c r="I41" s="4" t="s">
-        <v>161</v>
+        <v>58</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5" t="s">
-        <v>160</v>
+        <v>57</v>
       </c>
       <c r="L41" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>46196</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>155</v>
+        <v>52</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>220</v>
+        <v>134</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="5" t="s">
-        <v>221</v>
+        <v>135</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="H42" s="9">
         <v>4.26</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>161</v>
+        <v>58</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5" t="s">
-        <v>160</v>
+        <v>57</v>
       </c>
       <c r="L42" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="56" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="56" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>46249</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>222</v>
+        <v>136</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>223</v>
+        <v>137</v>
       </c>
       <c r="D43" s="3">
         <v>150</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>224</v>
+        <v>138</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>225</v>
+        <v>139</v>
       </c>
       <c r="H43" s="9"/>
       <c r="I43" s="4" t="s">
-        <v>223</v>
+        <v>137</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L43" s="5" t="s">
-        <v>21</v>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+      <c r="A44" s="11">
+        <v>46206</v>
+      </c>
+      <c r="B44" s="3"/>
+      <c r="C44" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D44" s="3">
+        <v>18</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H44" s="9"/>
+      <c r="I44" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L44" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+      <c r="A45" s="11">
+        <v>46197</v>
+      </c>
+      <c r="B45" s="3"/>
+      <c r="C45" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D45" s="3">
+        <v>18</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="H45" s="9"/>
+      <c r="I45" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L45" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+      <c r="A46" s="11">
+        <v>46283</v>
+      </c>
+      <c r="B46" s="3"/>
+      <c r="C46" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D46" s="3">
+        <v>45</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="H46" s="9"/>
+      <c r="I46" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="L46" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" ht="42" x14ac:dyDescent="0.2">
+      <c r="A47" s="11">
+        <v>46192</v>
+      </c>
+      <c r="B47" s="3"/>
+      <c r="C47" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D47" s="3">
+        <v>60</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="H47" s="9"/>
+      <c r="I47" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L47" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L42" xr:uid="{66042CC2-6DE3-41D0-9E68-E09A4B9870B3}"/>
+  <autoFilter ref="A1:L47" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -2863,54 +3046,54 @@
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="4" t="s">
-        <v>12</v>
+        <v>148</v>
       </c>
       <c r="D2" s="3">
         <v>40</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="4" t="s">
-        <v>13</v>
+        <v>149</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>45710</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="4" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="D3" s="3">
         <v>40</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="4" t="s">
-        <v>18</v>
+        <v>152</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
@@ -2919,54 +3102,54 @@
       </c>
       <c r="B4" s="3"/>
       <c r="C4" s="4" t="s">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="D4" s="3">
         <v>30</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="4" t="s">
-        <v>19</v>
+        <v>153</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>20</v>
+        <v>154</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>45794</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="4" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="D5" s="3">
         <v>40</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="4" t="s">
-        <v>18</v>
+        <v>152</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
@@ -2975,26 +3158,26 @@
       </c>
       <c r="B6" s="3"/>
       <c r="C6" s="4" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="D6" s="3">
         <v>30</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="4" t="s">
-        <v>19</v>
+        <v>153</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>20</v>
+        <v>154</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
@@ -3002,59 +3185,59 @@
         <v>45862</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>24</v>
+        <v>156</v>
       </c>
       <c r="D7" s="3">
         <v>120</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="4" t="s">
-        <v>25</v>
+        <v>157</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="4" t="s">
-        <v>24</v>
+        <v>156</v>
       </c>
       <c r="J7" s="4"/>
       <c r="K7" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>45892</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="4" t="s">
-        <v>27</v>
+        <v>158</v>
       </c>
       <c r="D8" s="3">
         <v>40</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="4" t="s">
-        <v>18</v>
+        <v>152</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -3063,26 +3246,26 @@
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="4" t="s">
-        <v>27</v>
+        <v>158</v>
       </c>
       <c r="D9" s="3">
         <v>30</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="4" t="s">
-        <v>19</v>
+        <v>153</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>20</v>
+        <v>154</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
@@ -3090,31 +3273,31 @@
         <v>45894</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>28</v>
+        <v>159</v>
       </c>
       <c r="D10" s="3">
         <v>120</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="4" t="s">
-        <v>29</v>
+        <v>160</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="4" t="s">
-        <v>28</v>
+        <v>159</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -3122,35 +3305,35 @@
         <v>45911</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>24</v>
+        <v>156</v>
       </c>
       <c r="D11" s="3">
         <v>40</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>33</v>
+        <v>161</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -3158,35 +3341,35 @@
         <v>45911</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>24</v>
+        <v>156</v>
       </c>
       <c r="D12" s="3">
         <v>24</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>38</v>
+        <v>162</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="4" t="s">
-        <v>39</v>
+        <v>163</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -3195,26 +3378,26 @@
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="4" t="s">
-        <v>40</v>
+        <v>164</v>
       </c>
       <c r="D13" s="3">
         <v>40</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="4" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
@@ -3222,143 +3405,143 @@
         <v>45957</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>42</v>
+        <v>165</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="D14" s="3">
         <v>27</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>44</v>
+        <v>167</v>
       </c>
       <c r="H14" s="6">
         <v>4.74</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>46</v>
+        <v>168</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L14" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>45957</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>47</v>
+        <v>169</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="D15" s="3">
         <v>28</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>48</v>
+        <v>170</v>
       </c>
       <c r="H15" s="6">
         <v>4.67</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>49</v>
+        <v>171</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>45957</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>50</v>
+        <v>172</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="D16" s="3">
         <v>24</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>51</v>
+        <v>173</v>
       </c>
       <c r="H16" s="6">
         <v>4.43</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>52</v>
+        <v>174</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L16" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>45957</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="D17" s="3">
         <v>25</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="H17" s="6">
         <v>4.43</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>55</v>
+        <v>176</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
@@ -3367,28 +3550,28 @@
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="D18" s="3">
         <v>24</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="4" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>57</v>
+        <v>178</v>
       </c>
       <c r="H18" s="6"/>
       <c r="I18" s="4" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L18" s="5" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
@@ -3397,28 +3580,28 @@
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="D19" s="3">
         <v>25</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="4" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="4" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
       <c r="J19" s="4"/>
       <c r="K19" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
@@ -3427,28 +3610,28 @@
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="D20" s="3">
         <v>27</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="4" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="4" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
       <c r="J20" s="4"/>
       <c r="K20" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L20" s="5" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
@@ -3457,28 +3640,28 @@
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="D21" s="3">
         <v>28</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="4" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="4" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
@@ -3486,35 +3669,35 @@
         <v>45958</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>60</v>
+        <v>181</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="D22" s="3">
         <v>23</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>61</v>
+        <v>182</v>
       </c>
       <c r="H22" s="6">
         <v>4.17</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>62</v>
+        <v>183</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
@@ -3522,35 +3705,35 @@
         <v>45958</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>63</v>
+        <v>184</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="D23" s="3">
         <v>25</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>64</v>
+        <v>185</v>
       </c>
       <c r="H23" s="6">
         <v>4.8099999999999996</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>65</v>
+        <v>186</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
@@ -3559,28 +3742,28 @@
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="D24" s="3">
         <v>23</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="4" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>57</v>
+        <v>178</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="4" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
       <c r="J24" s="4"/>
       <c r="K24" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
@@ -3589,64 +3772,64 @@
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="D25" s="3">
         <v>25</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="4" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>57</v>
+        <v>178</v>
       </c>
       <c r="H25" s="6"/>
       <c r="I25" s="4" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
       <c r="J25" s="4"/>
       <c r="K25" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>45959</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>42</v>
+        <v>165</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="D26" s="3">
         <v>26</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="H26" s="6">
         <v>4.2300000000000004</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>67</v>
+        <v>187</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>68</v>
+        <v>188</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
@@ -3654,33 +3837,33 @@
         <v>45959</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>47</v>
+        <v>169</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="D27" s="3">
         <v>26</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>69</v>
+        <v>189</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="4" t="s">
-        <v>70</v>
+        <v>190</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L27" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
@@ -3689,28 +3872,28 @@
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="D28" s="3">
         <v>26</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="4" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>71</v>
+        <v>191</v>
       </c>
       <c r="H28" s="6"/>
       <c r="I28" s="4" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
       <c r="J28" s="4"/>
       <c r="K28" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L28" s="5" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
@@ -3719,28 +3902,28 @@
       </c>
       <c r="B29" s="3"/>
       <c r="C29" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="D29" s="3">
         <v>26</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="4" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>71</v>
+        <v>191</v>
       </c>
       <c r="H29" s="6"/>
       <c r="I29" s="4" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
       <c r="J29" s="4"/>
       <c r="K29" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L29" s="5" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
@@ -3748,53 +3931,53 @@
         <v>45960</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>42</v>
+        <v>165</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="D30" s="3">
         <v>27</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="H30" s="6">
         <v>4.72</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>45960</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>50</v>
+        <v>172</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="D31" s="3">
         <v>19</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G31" s="4" t="s">
         <v>74</v>
@@ -3803,16 +3986,16 @@
         <v>4.7300000000000004</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>75</v>
+        <v>192</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L31" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
@@ -3821,28 +4004,28 @@
       </c>
       <c r="B32" s="3"/>
       <c r="C32" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="D32" s="3">
         <v>19</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="4" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>71</v>
+        <v>191</v>
       </c>
       <c r="H32" s="6"/>
       <c r="I32" s="4" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
       <c r="J32" s="4"/>
       <c r="K32" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L32" s="5" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
@@ -3851,28 +4034,28 @@
       </c>
       <c r="B33" s="3"/>
       <c r="C33" s="4" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="D33" s="3">
         <v>27</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="4" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="H33" s="6"/>
       <c r="I33" s="4" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
       <c r="J33" s="4"/>
       <c r="K33" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L33" s="5" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
@@ -3880,29 +4063,29 @@
         <v>45965</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>76</v>
+        <v>193</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="D34" s="3">
         <v>30</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="4" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="H34" s="6"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
       <c r="K34" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L34" s="5" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
@@ -3910,31 +4093,31 @@
         <v>45965</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>76</v>
+        <v>193</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="D35" s="3">
         <v>20</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="4" t="s">
-        <v>131</v>
+        <v>65</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>38</v>
+        <v>162</v>
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="4" t="s">
-        <v>81</v>
+        <v>195</v>
       </c>
       <c r="J35" s="4"/>
       <c r="K35" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L35" s="5" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
@@ -3942,29 +4125,29 @@
         <v>45965</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>76</v>
+        <v>193</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="D36" s="3">
         <v>30</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="4" t="s">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>83</v>
+        <v>197</v>
       </c>
       <c r="H36" s="6"/>
       <c r="I36" s="4"/>
       <c r="J36" s="4"/>
       <c r="K36" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L36" s="5" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
@@ -3972,37 +4155,37 @@
         <v>45968</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>86</v>
+        <v>199</v>
       </c>
       <c r="D37" s="3">
         <v>24</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="H37" s="6">
         <v>4.5</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>87</v>
+        <v>200</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L37" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
@@ -4010,65 +4193,65 @@
         <v>45968</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="C38" s="4"/>
       <c r="D38" s="3">
         <v>30</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>88</v>
+        <v>201</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>89</v>
+        <v>202</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="H38" s="6"/>
       <c r="I38" s="4" t="s">
-        <v>90</v>
+        <v>203</v>
       </c>
       <c r="J38" s="4"/>
       <c r="K38" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L38" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>45971</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>85</v>
+        <v>198</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>91</v>
+        <v>204</v>
       </c>
       <c r="D39" s="3">
         <v>15</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="4" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="H39" s="6"/>
       <c r="I39" s="4" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>92</v>
+        <v>205</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L39" s="5" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
@@ -4076,31 +4259,31 @@
         <v>45972</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>94</v>
+        <v>206</v>
       </c>
       <c r="D40" s="3">
         <v>30</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="4" t="s">
-        <v>95</v>
+        <v>207</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="H40" s="6"/>
       <c r="I40" s="4" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L40" s="5" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
@@ -4108,31 +4291,31 @@
         <v>45972</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>94</v>
+        <v>206</v>
       </c>
       <c r="D41" s="3">
         <v>30</v>
       </c>
       <c r="E41" s="5"/>
       <c r="F41" s="4" t="s">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>99</v>
+        <v>208</v>
       </c>
       <c r="H41" s="6"/>
       <c r="I41" s="4" t="s">
-        <v>100</v>
+        <v>209</v>
       </c>
       <c r="J41" s="4"/>
       <c r="K41" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L41" s="5" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
@@ -4140,65 +4323,65 @@
         <v>45972</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>94</v>
+        <v>206</v>
       </c>
       <c r="D42" s="3">
         <v>30</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="4" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>101</v>
+        <v>210</v>
       </c>
       <c r="H42" s="6"/>
       <c r="I42" s="4" t="s">
-        <v>102</v>
+        <v>211</v>
       </c>
       <c r="J42" s="4"/>
       <c r="K42" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L42" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>45986</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>103</v>
+        <v>212</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>104</v>
+        <v>213</v>
       </c>
       <c r="D43" s="3">
         <v>40</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>105</v>
+        <v>214</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>106</v>
+        <v>215</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>107</v>
+        <v>216</v>
       </c>
       <c r="H43" s="6"/>
       <c r="I43" s="4" t="s">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="J43" s="4"/>
       <c r="K43" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L43" s="5" t="s">
-        <v>98</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
@@ -4206,31 +4389,31 @@
         <v>45986</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>108</v>
+        <v>217</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>109</v>
+        <v>218</v>
       </c>
       <c r="D44" s="3">
         <v>12</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="4" t="s">
-        <v>110</v>
+        <v>219</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>111</v>
+        <v>220</v>
       </c>
       <c r="H44" s="6"/>
       <c r="I44" s="4" t="s">
-        <v>81</v>
+        <v>195</v>
       </c>
       <c r="J44" s="4"/>
       <c r="K44" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L44" s="5" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
@@ -4238,33 +4421,33 @@
         <v>45987</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>114</v>
+        <v>221</v>
       </c>
       <c r="D45" s="3">
         <v>30</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>115</v>
+        <v>222</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>116</v>
+        <v>90</v>
       </c>
       <c r="H45" s="6"/>
       <c r="I45" s="4"/>
       <c r="J45" s="4" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L45" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
@@ -4272,65 +4455,65 @@
         <v>45997</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>118</v>
+        <v>223</v>
       </c>
       <c r="D46" s="3">
         <v>20</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="4" t="s">
-        <v>119</v>
+        <v>224</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>120</v>
+        <v>225</v>
       </c>
       <c r="H46" s="6"/>
       <c r="I46" s="4" t="s">
-        <v>121</v>
+        <v>226</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="L46" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="28" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>45997</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>118</v>
+        <v>223</v>
       </c>
       <c r="D47" s="3">
         <v>20</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="4" t="s">
-        <v>123</v>
+        <v>227</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>124</v>
+        <v>228</v>
       </c>
       <c r="H47" s="6"/>
       <c r="I47" s="4" t="s">
-        <v>125</v>
+        <v>229</v>
       </c>
       <c r="J47" s="4"/>
       <c r="K47" s="5" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="L47" s="5" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
@@ -4338,33 +4521,33 @@
         <v>46000</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>108</v>
+        <v>217</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>126</v>
+        <v>230</v>
       </c>
       <c r="D48" s="3">
         <v>10</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>127</v>
+        <v>231</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>56</v>
+        <v>177</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>59</v>
+        <v>180</v>
       </c>
       <c r="H48" s="6"/>
       <c r="I48" s="4" t="s">
-        <v>58</v>
+        <v>179</v>
       </c>
       <c r="J48" s="4"/>
       <c r="K48" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="L48" s="5" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
@@ -4372,31 +4555,31 @@
         <v>46002</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>128</v>
+        <v>232</v>
       </c>
       <c r="D49" s="3">
         <v>120</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="4" t="s">
-        <v>129</v>
+        <v>42</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H49" s="6"/>
       <c r="I49" s="4" t="s">
-        <v>128</v>
+        <v>232</v>
       </c>
       <c r="J49" s="4"/>
       <c r="K49" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L49" s="5" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
@@ -4404,35 +4587,35 @@
         <v>46008</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>130</v>
+        <v>233</v>
       </c>
       <c r="D50" s="3">
         <v>120</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="4" t="s">
-        <v>129</v>
+        <v>42</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="H50" s="6"/>
       <c r="I50" s="4" t="s">
-        <v>130</v>
+        <v>233</v>
       </c>
       <c r="J50" s="4"/>
       <c r="K50" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="L50" s="5" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L50" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:L50" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>